--- a/cashier_practical_test_template.xlsx
+++ b/cashier_practical_test_template.xlsx
@@ -486,6 +486,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -493,6 +494,9 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -551,7 +555,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
@@ -597,7 +601,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
@@ -643,7 +647,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
@@ -689,7 +693,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
@@ -735,7 +739,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
@@ -750,6 +754,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
@@ -757,6 +762,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="34" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
@@ -783,12 +789,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Total Card Sales</t>
+          <t>Total Credit Sales</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Use SUMIF to total sales where Payment Type is Card.</t>
+          <t>Use SUMIF to total sales where Payment Type is Credit.</t>
         </is>
       </c>
       <c r="E23" s="7" t="n"/>
@@ -952,6 +958,7 @@
         <v>33000</v>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
@@ -972,12 +979,12 @@
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C26:D26"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="B34:E34"/>
     <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="C23:D23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
